--- a/ONCHO/Entomological survey Survey/Nigeria/2025/sites.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2025/sites.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO Thinkpad\Documents\InStrat\NTD Oncho\Taraba\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{EF619576-D797-2B42-88B3-E13F9A274CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4259EE-EFF3-4325-AC31-325F648F4C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12000" yWindow="0" windowWidth="12000" windowHeight="12900" xr2:uid="{7BE50F1A-DFCC-4B63-9F45-FF2F2A6DD4D6}"/>
+    <workbookView xWindow="-28575" yWindow="0" windowWidth="28800" windowHeight="15435" xr2:uid="{7BE50F1A-DFCC-4B63-9F45-FF2F2A6DD4D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$62</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="145">
   <si>
     <t>STATE</t>
   </si>
@@ -209,36 +209,9 @@
     <t>DANDIKULU</t>
   </si>
   <si>
-    <t>Ussa</t>
-  </si>
-  <si>
     <t>MEDEL PREDICTED STITES</t>
   </si>
   <si>
-    <t>Kurmi</t>
-  </si>
-  <si>
-    <t>Wukari</t>
-  </si>
-  <si>
-    <t>Sardauna</t>
-  </si>
-  <si>
-    <t>Ibi</t>
-  </si>
-  <si>
-    <t>Gashaka</t>
-  </si>
-  <si>
-    <t>Bali</t>
-  </si>
-  <si>
-    <t>Karim Lamido</t>
-  </si>
-  <si>
-    <t>Gassol</t>
-  </si>
-  <si>
     <t>SITE IDS</t>
   </si>
   <si>
@@ -383,30 +356,6 @@
     <t>USSA</t>
   </si>
   <si>
-    <t>Kwesati</t>
-  </si>
-  <si>
-    <t>Bente SAMA</t>
-  </si>
-  <si>
-    <t>Bantaje</t>
-  </si>
-  <si>
-    <t>Mayo-Ndaga</t>
-  </si>
-  <si>
-    <t>Maihula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sendirde </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kabri </t>
-  </si>
-  <si>
-    <t>Bambuka</t>
-  </si>
-  <si>
     <t>TAR_GAL_N_001</t>
   </si>
   <si>
@@ -455,9 +404,6 @@
     <t>KUKA WAZIRI</t>
   </si>
   <si>
-    <t>Ibi Rimi Uku I (ANGWAN GALADIMA)</t>
-  </si>
-  <si>
     <t>KURMA (IYAKA)</t>
   </si>
   <si>
@@ -498,6 +444,36 @@
   </si>
   <si>
     <t>GONO</t>
+  </si>
+  <si>
+    <t>KWESATI</t>
+  </si>
+  <si>
+    <t>BENTE SAMA</t>
+  </si>
+  <si>
+    <t>BANTAJE</t>
+  </si>
+  <si>
+    <t>MAYO-NDAGA</t>
+  </si>
+  <si>
+    <t>IBI RIMI UKU I (ANGWAN GALADIMA)</t>
+  </si>
+  <si>
+    <t>MAIHULA</t>
+  </si>
+  <si>
+    <t>BAMBUKA</t>
+  </si>
+  <si>
+    <t>SENDIRDE</t>
+  </si>
+  <si>
+    <t>KABRI</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -741,7 +717,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -798,12 +774,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{3938B651-D46A-48BA-A2D8-05D5BC138828}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1113,23 +1101,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD83EFE8-B67B-49E6-A276-5C214FFAD255}">
-  <dimension ref="A1:J59"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S61"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.08203125" customWidth="1"/>
-    <col min="3" max="3" width="25.2890625" customWidth="1"/>
-    <col min="4" max="4" width="23.26953125" customWidth="1"/>
-    <col min="5" max="5" width="20.84765625" customWidth="1"/>
-    <col min="6" max="6" width="18.6953125" customWidth="1"/>
-    <col min="7" max="7" width="17.08203125" customWidth="1"/>
-    <col min="8" max="8" width="21.38671875" customWidth="1"/>
-    <col min="9" max="9" width="26.09765625" customWidth="1"/>
-    <col min="10" max="10" width="20.4453125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="26.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" style="15" customWidth="1"/>
+    <col min="13" max="13" width="17.140625" customWidth="1"/>
+    <col min="15" max="15" width="17.140625" customWidth="1"/>
+    <col min="16" max="16" width="25.28515625" customWidth="1"/>
+    <col min="18" max="18" width="25.28515625" customWidth="1"/>
+    <col min="19" max="19" width="23.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -1156,10 +1149,25 @@
         <v>7</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="15">
         <v>1</v>
       </c>
@@ -1186,10 +1194,25 @@
         <v>11</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15">
         <v>2</v>
       </c>
@@ -1216,10 +1239,24 @@
         <v>11</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="K3"/>
+      <c r="M3"/>
+      <c r="O3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R3" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="36" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15">
         <v>3</v>
       </c>
@@ -1246,10 +1283,24 @@
         <v>11</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="K4"/>
+      <c r="M4"/>
+      <c r="O4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15">
         <v>4</v>
       </c>
@@ -1276,10 +1327,24 @@
         <v>11</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="K5"/>
+      <c r="M5"/>
+      <c r="O5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="15">
         <v>5</v>
       </c>
@@ -1306,10 +1371,22 @@
         <v>11</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P6" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="R6" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="S6" s="36" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="15">
         <v>6</v>
       </c>
@@ -1336,10 +1413,22 @@
         <v>11</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P7" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="19" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="15">
         <v>7</v>
       </c>
@@ -1366,10 +1455,22 @@
         <v>11</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="15">
         <v>8</v>
       </c>
@@ -1380,7 +1481,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="E9" s="37">
         <v>7.6394000000000002</v>
@@ -1396,10 +1497,22 @@
         <v>11</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="15">
         <v>9</v>
       </c>
@@ -1426,10 +1539,22 @@
         <v>11</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="15">
         <v>10</v>
       </c>
@@ -1456,10 +1581,22 @@
         <v>11</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S11" s="25" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="15">
         <v>11</v>
       </c>
@@ -1484,10 +1621,22 @@
         <v>24</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="15">
         <v>12</v>
       </c>
@@ -1514,10 +1663,22 @@
         <v>11</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="15">
         <v>13</v>
       </c>
@@ -1544,10 +1705,22 @@
         <v>11</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="R14" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="S14" s="25" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15">
         <v>14</v>
       </c>
@@ -1574,10 +1747,24 @@
         <v>11</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="K15"/>
+      <c r="M15"/>
+      <c r="O15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15">
         <v>15</v>
       </c>
@@ -1602,10 +1789,20 @@
         <v>24</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="K16"/>
+      <c r="M16"/>
+      <c r="O16"/>
+      <c r="P16"/>
+      <c r="R16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="S16" s="16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="15">
         <v>16</v>
       </c>
@@ -1632,10 +1829,16 @@
         <v>11</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="R17" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="S17" s="25" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="15">
         <v>17</v>
       </c>
@@ -1662,10 +1865,16 @@
         <v>11</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="R18" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="15">
         <v>18</v>
       </c>
@@ -1692,10 +1901,16 @@
         <v>11</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="15">
         <v>19</v>
       </c>
@@ -1722,10 +1937,16 @@
         <v>11</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="15">
         <v>20</v>
       </c>
@@ -1752,10 +1973,16 @@
         <v>11</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="15">
         <v>21</v>
       </c>
@@ -1766,7 +1993,7 @@
         <v>32</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="E22" s="37">
         <v>8.5330399999999997</v>
@@ -1782,10 +2009,16 @@
         <v>11</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="15">
         <v>22</v>
       </c>
@@ -1812,10 +2045,16 @@
         <v>11</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="15">
         <v>23</v>
       </c>
@@ -1842,10 +2081,16 @@
         <v>11</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="R24" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="15">
         <v>24</v>
       </c>
@@ -1856,7 +2101,7 @@
         <v>38</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="E25" s="37">
         <v>9.4654600000000002</v>
@@ -1872,10 +2117,16 @@
         <v>11</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="R25" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="15">
         <v>25</v>
       </c>
@@ -1902,10 +2153,16 @@
         <v>11</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="R26" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="S26" s="19" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="15">
         <v>26</v>
       </c>
@@ -1916,7 +2173,7 @@
         <v>38</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="E27" s="37">
         <v>9.3929399999999994</v>
@@ -1932,10 +2189,16 @@
         <v>11</v>
       </c>
       <c r="J27" s="22" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="R27" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="15">
         <v>27</v>
       </c>
@@ -1946,7 +2209,7 @@
         <v>38</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="E28" s="37">
         <v>9.46922</v>
@@ -1962,10 +2225,16 @@
         <v>11</v>
       </c>
       <c r="J28" s="22" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="R28" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="S28" s="34" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="15">
         <v>28</v>
       </c>
@@ -1992,10 +2261,16 @@
         <v>11</v>
       </c>
       <c r="J29" s="22" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+      <c r="R29" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="15">
         <v>29</v>
       </c>
@@ -2020,10 +2295,16 @@
         <v>24</v>
       </c>
       <c r="J30" s="22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="R30" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="S30" s="25" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="15">
         <v>30</v>
       </c>
@@ -2034,7 +2315,7 @@
         <v>38</v>
       </c>
       <c r="D31" s="25" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="E31" s="37">
         <v>9.43689</v>
@@ -2050,10 +2331,16 @@
         <v>11</v>
       </c>
       <c r="J31" s="22" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="R31" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="15">
         <v>31</v>
       </c>
@@ -2080,10 +2367,16 @@
         <v>11</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="R32" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" s="15">
         <v>32</v>
       </c>
@@ -2094,7 +2387,7 @@
         <v>44</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="E33" s="37">
         <v>6.5464900000000004</v>
@@ -2110,10 +2403,16 @@
         <v>11</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="R33" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S33" s="19" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="15">
         <v>33</v>
       </c>
@@ -2140,10 +2439,20 @@
         <v>11</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="K34"/>
+      <c r="M34"/>
+      <c r="O34"/>
+      <c r="P34"/>
+      <c r="R34" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="S34" s="25" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" s="15">
         <v>34</v>
       </c>
@@ -2170,10 +2479,16 @@
         <v>11</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="R35" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="S35" s="25" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" s="15">
         <v>35</v>
       </c>
@@ -2200,10 +2515,16 @@
         <v>11</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="R36" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="S36" s="25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" s="15">
         <v>36</v>
       </c>
@@ -2228,10 +2549,16 @@
         <v>24</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="R37" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="S37" s="25" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="15">
         <v>37</v>
       </c>
@@ -2239,7 +2566,7 @@
         <v>8</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>50</v>
@@ -2258,10 +2585,16 @@
         <v>11</v>
       </c>
       <c r="J38" s="22" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="R38" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="S38" s="16" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" s="15">
         <v>38</v>
       </c>
@@ -2288,10 +2621,16 @@
         <v>11</v>
       </c>
       <c r="J39" s="22" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="R39" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" s="15">
         <v>39</v>
       </c>
@@ -2299,7 +2638,7 @@
         <v>8</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>52</v>
@@ -2318,10 +2657,16 @@
         <v>11</v>
       </c>
       <c r="J40" s="22" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="R40" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" s="15">
         <v>40</v>
       </c>
@@ -2332,7 +2677,7 @@
         <v>53</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="E41" s="37">
         <v>8.1268799999999999</v>
@@ -2346,10 +2691,16 @@
         <v>24</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="R41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S41" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" s="15">
         <v>41</v>
       </c>
@@ -2360,7 +2711,7 @@
         <v>53</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E42" s="37">
         <v>7.9092799999999999</v>
@@ -2376,10 +2727,16 @@
         <v>11</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="R42" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" s="15">
         <v>42</v>
       </c>
@@ -2406,10 +2763,16 @@
         <v>11</v>
       </c>
       <c r="J43" s="14" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S43" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="15">
         <v>43</v>
       </c>
@@ -2417,10 +2780,10 @@
         <v>8</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="E44" s="37">
         <v>7.18546</v>
@@ -2431,13 +2794,23 @@
       <c r="G44" s="3"/>
       <c r="H44" s="5"/>
       <c r="I44" s="38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="K44"/>
+      <c r="M44"/>
+      <c r="O44"/>
+      <c r="P44"/>
+      <c r="R44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S44" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" s="15">
         <v>44</v>
       </c>
@@ -2445,10 +2818,10 @@
         <v>8</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="E45" s="37">
         <v>7.2979200000000004</v>
@@ -2460,10 +2833,16 @@
       <c r="H45" s="5"/>
       <c r="I45" s="39"/>
       <c r="J45" s="14" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="R45" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S45" s="25" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" s="15">
         <v>45</v>
       </c>
@@ -2471,25 +2850,31 @@
         <v>8</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E46" s="37">
         <v>7.84131</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="5"/>
       <c r="I46" s="39"/>
       <c r="J46" s="14" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="R46" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="S46" s="19" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" s="15">
         <v>46</v>
       </c>
@@ -2497,10 +2882,10 @@
         <v>8</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="E47" s="37">
         <v>6.8639700000000001</v>
@@ -2512,10 +2897,16 @@
       <c r="H47" s="5"/>
       <c r="I47" s="39"/>
       <c r="J47" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+      <c r="R47" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="S47" s="19" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" s="15">
         <v>47</v>
       </c>
@@ -2523,10 +2914,10 @@
         <v>8</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D48" s="34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E48" s="37">
         <v>8.4078189999999999</v>
@@ -2538,10 +2929,16 @@
       <c r="H48" s="5"/>
       <c r="I48" s="39"/>
       <c r="J48" s="14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="R48" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S48" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="15">
         <v>48</v>
       </c>
@@ -2549,10 +2946,10 @@
         <v>8</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="E49" s="37">
         <v>7.7786900000000001</v>
@@ -2564,10 +2961,16 @@
       <c r="H49" s="5"/>
       <c r="I49" s="39"/>
       <c r="J49" s="14" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="R49" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S49" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="15">
         <v>49</v>
       </c>
@@ -2575,10 +2978,10 @@
         <v>8</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="E50" s="37"/>
       <c r="F50" s="37"/>
@@ -2586,10 +2989,16 @@
       <c r="H50" s="5"/>
       <c r="I50" s="39"/>
       <c r="J50" s="14" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="R50" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="S50" s="25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="15">
         <v>50</v>
       </c>
@@ -2597,10 +3006,10 @@
         <v>8</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="E51" s="37">
         <v>9.4357699999999998</v>
@@ -2612,10 +3021,16 @@
       <c r="H51" s="5"/>
       <c r="I51" s="39"/>
       <c r="J51" s="14" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="R51" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S51" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="15">
         <v>51</v>
       </c>
@@ -2623,10 +3038,10 @@
         <v>8</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="E52" s="37">
         <v>8.7610010000000003</v>
@@ -2638,10 +3053,16 @@
       <c r="H52" s="5"/>
       <c r="I52" s="39"/>
       <c r="J52" s="14" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="R52" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="S52" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="15">
         <v>52</v>
       </c>
@@ -2649,10 +3070,10 @@
         <v>8</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="E53" s="37">
         <v>6.6919599999999999</v>
@@ -2664,10 +3085,16 @@
       <c r="H53" s="5"/>
       <c r="I53" s="39"/>
       <c r="J53" s="14" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="R53" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="S53" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="15">
         <v>53</v>
       </c>
@@ -2678,7 +3105,7 @@
         <v>9</v>
       </c>
       <c r="D54" s="35" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="E54" s="26">
         <v>8.8032900000000005</v>
@@ -2690,10 +3117,16 @@
       <c r="H54" s="28"/>
       <c r="I54" s="32"/>
       <c r="J54" s="18" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+      <c r="R54" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="S54" s="40" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="15">
         <v>54</v>
       </c>
@@ -2704,7 +3137,7 @@
         <v>13</v>
       </c>
       <c r="D55" s="36" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="E55" s="37">
         <v>7.8507100000000003</v>
@@ -2716,10 +3149,16 @@
       <c r="H55" s="28"/>
       <c r="I55" s="32"/>
       <c r="J55" s="18" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+      <c r="R55" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="S55" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="15">
         <v>55</v>
       </c>
@@ -2730,7 +3169,7 @@
         <v>22</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="E56" s="26">
         <v>7.4470499999999999</v>
@@ -2742,10 +3181,16 @@
       <c r="H56" s="28"/>
       <c r="I56" s="32"/>
       <c r="J56" s="18" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+      <c r="R56" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="S56" s="19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="15">
         <v>56</v>
       </c>
@@ -2756,7 +3201,7 @@
         <v>22</v>
       </c>
       <c r="D57" s="25" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="E57" s="37">
         <v>7.8493300000000001</v>
@@ -2768,10 +3213,16 @@
       <c r="H57" s="28"/>
       <c r="I57" s="32"/>
       <c r="J57" s="18" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+      <c r="R57" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="S57" s="25" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="15">
         <v>57</v>
       </c>
@@ -2782,7 +3233,7 @@
         <v>38</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="E58" s="26">
         <v>9.1817499999999992</v>
@@ -2794,10 +3245,16 @@
       <c r="H58" s="29"/>
       <c r="I58" s="33"/>
       <c r="J58" s="18" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+      <c r="R58" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="S58" s="25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="15">
         <v>58</v>
       </c>
@@ -2808,7 +3265,7 @@
         <v>44</v>
       </c>
       <c r="D59" s="25" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="E59" s="37"/>
       <c r="F59" s="37"/>
@@ -2816,19 +3273,54 @@
       <c r="H59" s="28"/>
       <c r="I59" s="31"/>
       <c r="J59" s="18" t="s">
-        <v>148</v>
+        <v>130</v>
+      </c>
+      <c r="R59" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C60" t="s">
+        <v>144</v>
+      </c>
+      <c r="D60" t="s">
+        <v>144</v>
+      </c>
+      <c r="R60" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C61" t="s">
+        <v>144</v>
+      </c>
+      <c r="D61" t="s">
+        <v>144</v>
+      </c>
+      <c r="R61" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J62" xr:uid="{FD83EFE8-B67B-49E6-A276-5C214FFAD255}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J62">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J59">
       <sortCondition ref="A1:A62"/>
     </sortState>
   </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="R2:S59">
+    <sortCondition ref="R2:R59"/>
+    <sortCondition ref="S2:S59"/>
+  </sortState>
   <mergeCells count="1">
     <mergeCell ref="I44:I53"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="S60:S1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>